--- a/Table2_Supplementary.xlsx
+++ b/Table2_Supplementary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/THESIS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31BED540-870A-4D76-9B75-751B57A138B6}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23F7AD32-13FB-42C9-8AE1-C01CAE459C5D}"/>
   <bookViews>
-    <workbookView xWindow="9518" yWindow="0" windowWidth="9765" windowHeight="11363" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="205">
   <si>
     <t>table_ID</t>
   </si>
@@ -154,9 +154,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>HOMODIMER</t>
-  </si>
-  <si>
     <t>Linb_2r_dgp_K_all</t>
   </si>
   <si>
@@ -451,27 +448,15 @@
     <t>cmebl_1r_cdh_U_all</t>
   </si>
   <si>
-    <t>ldex</t>
-  </si>
-  <si>
     <t>K01560</t>
   </si>
   <si>
-    <t>ldex_1</t>
-  </si>
-  <si>
     <t xml:space="preserve"> TATTTCTGTGGATGCTGTTCGAGTGtayaarcc</t>
   </si>
   <si>
-    <t>ldex_1f_cdh_U_all</t>
-  </si>
-  <si>
     <t xml:space="preserve"> CTGGACGATTAATCCAACCTGTAGGraanccraa</t>
   </si>
   <si>
-    <t>ldex_1r_cdh_U_all</t>
-  </si>
-  <si>
     <t>cate</t>
   </si>
   <si>
@@ -551,12 +536,6 @@
   </si>
   <si>
     <t>p_ID</t>
-  </si>
-  <si>
-    <t>5_fr</t>
-  </si>
-  <si>
-    <t>HOMODIMER, 5_r</t>
   </si>
   <si>
     <t>Details</t>
@@ -674,6 +653,24 @@
   </si>
   <si>
     <t>Look Up Table</t>
+  </si>
+  <si>
+    <t>dehII</t>
+  </si>
+  <si>
+    <t>dehII_1</t>
+  </si>
+  <si>
+    <t>dehII_1f_cdh_U_all</t>
+  </si>
+  <si>
+    <t>dehII_1r_cdh_U_all</t>
+  </si>
+  <si>
+    <t>Linb_5r</t>
+  </si>
+  <si>
+    <t>Linb_5f</t>
   </si>
 </sst>
 </file>
@@ -745,10 +742,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1044,7 +1037,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.45">
@@ -1097,7 +1090,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
@@ -1434,23 +1427,21 @@
       <c r="S8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="T8" s="2"/>
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="U8" s="2">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2">
-        <v>0</v>
-      </c>
-      <c r="W8" s="2">
-        <v>0</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.45">
@@ -1476,13 +1467,13 @@
         <v>28</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K9" s="2">
         <v>9</v>
@@ -1525,7 +1516,7 @@
         <v>6</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.45">
@@ -1551,13 +1542,13 @@
         <v>28</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K10" s="2">
         <v>27</v>
@@ -1600,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.45">
@@ -1614,7 +1605,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2">
         <v>40</v>
@@ -1623,16 +1614,16 @@
         <v>27</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K11" s="2">
         <v>4</v>
@@ -1662,7 +1653,7 @@
         <v>41</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="U11" s="2">
         <v>0</v>
@@ -1677,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.45">
@@ -1691,7 +1682,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2">
         <v>40</v>
@@ -1700,16 +1691,16 @@
         <v>27</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K12" s="2">
         <v>2</v>
@@ -1752,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.45">
@@ -1766,7 +1757,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
@@ -1775,16 +1766,16 @@
         <v>27</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K13" s="2">
         <v>4</v>
@@ -1814,7 +1805,7 @@
         <v>41</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="U13" s="2">
         <v>0</v>
@@ -1829,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.45">
@@ -1843,7 +1834,7 @@
         <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
@@ -1852,16 +1843,16 @@
         <v>27</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K14" s="2">
         <v>4</v>
@@ -1891,7 +1882,7 @@
         <v>41</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="U14" s="2">
         <v>0</v>
@@ -1906,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.45">
@@ -1920,25 +1911,25 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2">
         <v>23</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K15" s="2">
         <v>8</v>
@@ -1967,9 +1958,7 @@
       <c r="S15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="T15" s="2"/>
       <c r="U15" s="2">
         <v>11</v>
       </c>
@@ -1983,7 +1972,7 @@
         <v>29</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.45">
@@ -1997,25 +1986,25 @@
         <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2">
         <v>23</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K16" s="2">
         <v>16</v>
@@ -2044,9 +2033,7 @@
       <c r="S16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="T16" s="2"/>
       <c r="U16" s="2">
         <v>89</v>
       </c>
@@ -2060,7 +2047,7 @@
         <v>31</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.45">
@@ -2074,25 +2061,25 @@
         <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2">
         <v>23</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K17" s="2">
         <v>4</v>
@@ -2122,7 +2109,7 @@
         <v>32</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U17" s="2">
         <v>143</v>
@@ -2137,7 +2124,7 @@
         <v>43</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.45">
@@ -2151,25 +2138,25 @@
         <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2">
         <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K18" s="2">
         <v>16</v>
@@ -2212,7 +2199,7 @@
         <v>29</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.45">
@@ -2226,25 +2213,25 @@
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2">
         <v>23</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K19" s="2">
         <v>8</v>
@@ -2287,7 +2274,7 @@
         <v>17</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.45">
@@ -2301,25 +2288,25 @@
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2">
         <v>23</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K20" s="2">
         <v>8</v>
@@ -2349,7 +2336,7 @@
         <v>32</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U20" s="2">
         <v>60</v>
@@ -2364,7 +2351,7 @@
         <v>47</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.45">
@@ -2378,25 +2365,25 @@
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E21" s="2">
         <v>23</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K21" s="2">
         <v>8</v>
@@ -2439,7 +2426,7 @@
         <v>55</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.45">
@@ -2453,25 +2440,25 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2">
         <v>23</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K22" s="2">
         <v>4</v>
@@ -2514,7 +2501,7 @@
         <v>31</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.45">
@@ -2528,25 +2515,25 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2">
         <v>22</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K23" s="2">
         <v>0</v>
@@ -2576,7 +2563,7 @@
         <v>32</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U23" s="2">
         <v>11</v>
@@ -2591,7 +2578,7 @@
         <v>26</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.45">
@@ -2605,25 +2592,25 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2">
         <v>22</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K24" s="2">
         <v>0</v>
@@ -2666,7 +2653,7 @@
         <v>23</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.45">
@@ -2680,25 +2667,25 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
@@ -2728,7 +2715,7 @@
         <v>32</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U25" s="2">
         <v>11</v>
@@ -2743,7 +2730,7 @@
         <v>26</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.45">
@@ -2757,25 +2744,25 @@
         <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2">
         <v>22</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K26" s="2">
         <v>0</v>
@@ -2818,7 +2805,7 @@
         <v>23</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.45">
@@ -2826,10 +2813,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>26</v>
@@ -2841,16 +2828,16 @@
         <v>27</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K27" s="2">
         <v>8</v>
@@ -2893,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.45">
@@ -2901,10 +2888,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>26</v>
@@ -2916,16 +2903,16 @@
         <v>27</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K28" s="2">
         <v>8</v>
@@ -2968,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.45">
@@ -2976,10 +2963,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>26</v>
@@ -2991,16 +2978,16 @@
         <v>27</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K29" s="2">
         <v>16</v>
@@ -3043,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.45">
@@ -3051,10 +3038,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>26</v>
@@ -3066,16 +3053,16 @@
         <v>27</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K30" s="2">
         <v>16</v>
@@ -3118,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.45">
@@ -3126,13 +3113,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="2">
         <v>19</v>
@@ -3141,16 +3128,16 @@
         <v>27</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K31" s="2">
         <v>4</v>
@@ -3193,7 +3180,7 @@
         <v>4</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.45">
@@ -3201,13 +3188,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2">
         <v>19</v>
@@ -3216,16 +3203,16 @@
         <v>27</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K32" s="2">
         <v>16</v>
@@ -3255,7 +3242,7 @@
         <v>41</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U32" s="2">
         <v>2</v>
@@ -3270,7 +3257,7 @@
         <v>1</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.45">
@@ -3278,10 +3265,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>26</v>
@@ -3290,19 +3277,19 @@
         <v>12</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K33" s="2">
         <v>8</v>
@@ -3332,7 +3319,7 @@
         <v>41</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U33" s="2">
         <v>5</v>
@@ -3347,7 +3334,7 @@
         <v>1</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.45">
@@ -3355,10 +3342,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>26</v>
@@ -3367,19 +3354,19 @@
         <v>12</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K34" s="2">
         <v>16</v>
@@ -3409,7 +3396,7 @@
         <v>41</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U34" s="2">
         <v>5</v>
@@ -3424,7 +3411,7 @@
         <v>3</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.45">
@@ -3432,31 +3419,31 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K35" s="2">
         <v>6</v>
@@ -3499,7 +3486,7 @@
         <v>4</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.45">
@@ -3507,31 +3494,31 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K36" s="2">
         <v>16</v>
@@ -3561,7 +3548,7 @@
         <v>41</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U36" s="2">
         <v>0</v>
@@ -3576,7 +3563,7 @@
         <v>2</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.45">
@@ -3584,10 +3571,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>26</v>
@@ -3602,13 +3589,13 @@
         <v>28</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K37" s="2">
         <v>3</v>
@@ -3651,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.45">
@@ -3659,10 +3646,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>26</v>
@@ -3677,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K38" s="2">
         <v>2</v>
@@ -3726,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.45">
@@ -3734,10 +3721,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>26</v>
@@ -3752,13 +3739,13 @@
         <v>28</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K39" s="2">
         <v>3</v>
@@ -3801,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.45">
@@ -3809,10 +3796,10 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>26</v>
@@ -3827,13 +3814,13 @@
         <v>28</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K40" s="2">
         <v>2</v>
@@ -3876,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.45">
@@ -3884,10 +3871,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>26</v>
@@ -3896,19 +3883,19 @@
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K41" s="2">
         <v>6</v>
@@ -3951,7 +3938,7 @@
         <v>8</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.45">
@@ -3959,10 +3946,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>26</v>
@@ -3971,19 +3958,19 @@
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K42" s="2">
         <v>16</v>
@@ -4026,7 +4013,7 @@
         <v>11</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.45">
@@ -4034,10 +4021,10 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>26</v>
@@ -4046,19 +4033,19 @@
         <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K43" s="2">
         <v>4</v>
@@ -4101,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.45">
@@ -4109,10 +4096,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>26</v>
@@ -4121,19 +4108,19 @@
         <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K44" s="2">
         <v>16</v>
@@ -4176,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>147</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.45">
@@ -4184,10 +4171,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>26</v>
@@ -4196,19 +4183,19 @@
         <v>9</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K45" s="2">
         <v>2</v>
@@ -4251,7 +4238,7 @@
         <v>7</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.45">
@@ -4259,10 +4246,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>26</v>
@@ -4271,19 +4258,19 @@
         <v>9</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K46" s="2">
         <v>4</v>
@@ -4312,9 +4299,7 @@
       <c r="S46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T46" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="T46" s="2"/>
       <c r="U46" s="2">
         <v>0</v>
       </c>
@@ -4328,7 +4313,7 @@
         <v>7</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.45">
@@ -4336,10 +4321,10 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>26</v>
@@ -4348,19 +4333,19 @@
         <v>9</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K47" s="2">
         <v>16</v>
@@ -4403,7 +4388,7 @@
         <v>4</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.45">
@@ -4411,10 +4396,10 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>26</v>
@@ -4429,13 +4414,13 @@
         <v>28</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="K48" s="2">
         <v>9</v>
@@ -4465,7 +4450,7 @@
         <v>41</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="U48" s="2">
         <v>0</v>
@@ -4480,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.45">
@@ -4488,10 +4473,10 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>26</v>
@@ -4506,13 +4491,13 @@
         <v>28</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="K49" s="2">
         <v>0</v>
@@ -4555,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.45">
@@ -4563,10 +4548,10 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>26</v>
@@ -4581,13 +4566,13 @@
         <v>28</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="K50" s="2">
         <v>9</v>
@@ -4630,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.45">
@@ -4638,10 +4623,10 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>26</v>
@@ -4656,13 +4641,13 @@
         <v>28</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="K51" s="2">
         <v>0</v>
@@ -4692,7 +4677,7 @@
         <v>41</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="U51" s="2">
         <v>1</v>
@@ -4707,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.45">
@@ -4721,25 +4706,25 @@
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E52" s="2">
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="K52" s="2">
         <v>8</v>
@@ -4782,7 +4767,7 @@
         <v>47</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.45">
@@ -4796,25 +4781,25 @@
         <v>25</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E53" s="2">
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="K53" s="2">
         <v>8</v>
@@ -4857,7 +4842,7 @@
         <v>8</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.45">
@@ -4902,31 +4887,31 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
@@ -4934,7 +4919,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
@@ -4942,7 +4927,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
@@ -4950,7 +4935,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
@@ -4958,15 +4943,15 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
@@ -4974,7 +4959,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
@@ -4982,7 +4967,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
@@ -4990,7 +4975,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
@@ -4998,7 +4983,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
@@ -5006,7 +4991,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
@@ -5014,7 +4999,7 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
@@ -5022,7 +5007,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
@@ -5030,7 +5015,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
@@ -5038,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
@@ -5046,7 +5031,7 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
@@ -5054,7 +5039,7 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
@@ -5062,7 +5047,7 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -5070,7 +5055,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
@@ -5078,7 +5063,7 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -5086,7 +5071,7 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
@@ -5094,7 +5079,7 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
@@ -5102,7 +5087,7 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Table2_Supplementary.xlsx
+++ b/Table2_Supplementary.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="163" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23F7AD32-13FB-42C9-8AE1-C01CAE459C5D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1410" yWindow="675" windowWidth="8693" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
